--- a/光伏配储项目/电价数据/2026/猎德站.xlsx
+++ b/光伏配储项目/电价数据/2026/猎德站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51471</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.75254</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57892</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.58921</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.52385</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.51427</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43811</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45502</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.42203</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42192</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42658</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40977</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39539</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40107</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42368</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41302</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38528</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41735</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39245</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42113</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.4143</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42432</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.4119</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44265</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27752</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12229</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10019</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.11118</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.10296</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.12181</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.04382</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.09326999999999999</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.14741</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.13061</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.10375</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09072</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.06681000000000001</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.11962</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.10019</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14693</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21405</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23584</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25421</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.22313</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.13516</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.29079</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.13137</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.28484</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.2789</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.28014</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.2145</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5883400000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.45788</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.5095299999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.63414</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.55883</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.4418</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.43049</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5652699999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.45232</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.60884</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.8069700000000001</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.62138</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.64949</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.75073</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.99866</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41466</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.66276</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58463</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.77208</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.30412</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.62497</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.60842</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.52277</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48083</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47155</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41631</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42603</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6962200000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.79613</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.59423</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.61294</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48168</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5174099999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50461</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5057200000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48676</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40094</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46892</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37397</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41721</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.47669</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.53395</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.41371</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42743</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.44153</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5085500000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.48875</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.75627</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.98799</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.6535</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.8155800000000001</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.7511</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.6546799999999999</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.72654</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.5662200000000001</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.91218</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.84251</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28195</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.42244</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.49712</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.48383</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5254</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.9909199999999999</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.65364</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.57616</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.5825</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.58038</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.43777</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.41009</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.7847999999999999</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.5621</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.49126</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.57462</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.55986</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6755</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.60003</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.72589</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.77334</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.5017699999999999</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.44656</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.39017</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43811</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43157</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40898</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37771</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33471</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5122899999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.45785</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.46495</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45241</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41751</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.38528</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43165</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44762</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47366</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44776</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44203</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39698</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.30058</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.30176</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.21965</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27444</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.5507300000000001</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.49636</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.04093</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.61614</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.64039</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.49792</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.51558</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.49696</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.56469</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.6434099999999999</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.65252</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.4943</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.39419</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.40424</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5073299999999999</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.41437</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.47173</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.41416</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.47397</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.57635</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38325</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.53764</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.61948</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.61761</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.58788</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.47566</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42872</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.49548</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.40874</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.45966</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.44081</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.46444</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44944</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.40219</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.42687</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.40584</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39808</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40192</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34214</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52599</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.37845</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45354</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.39513</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26642</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.09522</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.23739</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.2154</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.23378</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.54338</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.42312</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.21419</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.49479</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.44683</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.54462</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.50724</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.48386</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.37735</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.25973</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.15357</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.29078</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.36635</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.28905</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.46338</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.39586</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.39487</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32813</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38234</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04466</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.28692</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03124</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04654999999999999</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.18205</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.22071</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.20405</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15788</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04585</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04972</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.0384</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04568</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04364</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21824</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05668</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04922</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04307</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-8.000000000000001e-05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.06756000000000001</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.40423</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.04071</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.10124</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29015</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38702</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39143</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39927</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40973</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46674</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39566</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39901</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41523</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35009</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6555</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39765</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44105</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4189</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.41836</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10255</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04353</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04565</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.07275</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.10887</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.4476</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.008670000000000001</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04577000000000001</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.0437</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04552</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04344</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04521</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04528</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04362</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.18019</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.17876</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.0447</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04995</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04974</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04738000000000001</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04787</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19981</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14275</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29471</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30459</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29498</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29291</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29235</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29684</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26878</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29384</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33494</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31692</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40335</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28085</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.2709</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15861</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17091</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14769</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15857</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23611</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21399</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28567</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29076</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28085</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28044</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27103</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28093</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42839</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45678</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41869</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41553</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15647</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50769</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62205</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78104</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92043</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49459</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9144600000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8634299999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29664</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88819</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63176</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18778</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86888</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5274</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33154</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0334</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53146</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79153</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52695</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7735299999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77798</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8768400000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87415</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49367</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39919</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40058</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45054</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20768</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87888</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5510499999999999</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62253</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5385</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.4979</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45592</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.4372799999999999</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44996</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38836</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45271</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41984</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39978</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38499</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41405</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43284</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38979</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45058</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39926</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39805</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5829099999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42489</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5945900000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.59882</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.67943</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47008</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41563</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5783200000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44879</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8637100000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.61697</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8832100000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.83745</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8616900000000001</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43893</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.70328</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.42851</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27891</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34298</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4074</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.40997</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.44886</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41227</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35272</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9161</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46203</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.48852</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40339</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.45791</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40748</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39744</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49548</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29052</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16855</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26246</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19887</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27705</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19162</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25553</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27636</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43586</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44823</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41814</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39784</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5892000000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88789</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.58009</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14986</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69778</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78822</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6551900000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57116</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44467</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44942</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.4996</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43901</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43515</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41412</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42141</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49616</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41212</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43325</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41014</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43335</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42469</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44656</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42275</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43072</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41212</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41228</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42011</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39635</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49256</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36187</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.1366</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.57072</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24983</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.03814</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.20409</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.24103</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.28774</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.21974</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30211</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26076</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25516</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30814</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28412</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28574</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29203</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29197</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40355</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39859</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.56864</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.4591</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.80259</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.4611</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43393</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.49596</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38373</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32187</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.41833</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39367</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.27734</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.01655</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.28951</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.2359</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.15022</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.15231</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14182</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14341</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14247</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25865</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14292</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26443</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26248</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14486</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.13514</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11342</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11233</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.1473</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14306</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14861</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28774</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.37627</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4452</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39663</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38718</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39426</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44389</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43533</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43476</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.43962</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44285</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40103</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39629</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34689</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53186</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46397</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42019</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41245</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36821</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37815</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29519</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28175</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27052</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26616</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20761</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.25226</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24447</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26965</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28866</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.2889</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24202</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28568</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.38328</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.36473</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.25513</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41278</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36623</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3683999999999999</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38326</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.3587</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41369</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.35345</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.39442</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.38982</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43158</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42663</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.66413</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.4146</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.79534</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.7885</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24717</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.72715</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.93013</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.40295</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30653</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.6092000000000001</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41942</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43196</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43569</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42046</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.69196</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.51487</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.2286</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37772</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34692</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.46492</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28323</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38325</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.3776600000000001</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34886</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36553</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38314</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.41238</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41075</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37512</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6565</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.76001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.4497</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.2819700000000001</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45457</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34341</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41046</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36503</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26546</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28044</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28213</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20196</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25258</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28159</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21911</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26024</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28568</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27871</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28967</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29084</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36436</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.42615</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.37233</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40646</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.63234</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5943200000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.59349</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46636</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.74891</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47654</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.79555</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.42918</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48647</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39734</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.46407</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42735</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41661</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35882</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48545</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.52565</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47777</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.47878</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41436</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39497</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40769</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40565</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41375</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40804</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40622</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39208</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41536</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41407</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38809</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39706</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39747</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.40922</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39689</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.4448</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.4935</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44554</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.5121</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44474</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46184</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37346</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.41945</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.45422</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.45009</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5349400000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43607</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28651</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.56575</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.05379</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41109</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43481</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48862</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43551</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.49489</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50001</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.53446</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6811699999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.70324</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.76288</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.49528</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.79832</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5791900000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52313</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8252200000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7732899999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62425</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67372</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44343</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47145</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.47935</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47302</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46651</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41488</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5482899999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42576</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4387</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45265</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43421</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.4426</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41572</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39686</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45054</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39465</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39389</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37627</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3788</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36439</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36818</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39172</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37414</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.21008</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.68526</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44568</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39201</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.45719</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11267</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18133</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41472</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36708</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43213</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41478</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41317</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38209</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38707</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40513</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40637</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.3682</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39392</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39676</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39034</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37561</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36179</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.43983</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39049</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27247</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22164</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28588</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23156</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28375</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25067</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25106</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13487</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24457</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04216</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.24998</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.2825299999999999</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17232</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18868</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27447</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23397</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25645</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26226</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23189</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27538</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28302</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28319</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.38253</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.39345</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.39808</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.39805</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34656</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.29961</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30092</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.29702</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30191</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.29741</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28057</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.27569</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.18634</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24375</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.24381</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00063</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.01253</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04939</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.13273</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.00513</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03938000000000001</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01456</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.0406</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03793999999999999</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04809</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04765</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02458</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.0269</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04921</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00153</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.23829</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04923</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02434</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04935</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03890999999999999</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18199</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.23616</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.26648</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27989</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.28244</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28764</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.38571</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.14554</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.26308</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.59114</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.43824</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.29332</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.28951</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.29784</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.28108</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.28207</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.40661</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.28847</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.67027</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.8188799999999999</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.7930900000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.6335299999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.26227</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.01522</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.2336</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.20318</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.23503</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.23059</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.21384</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2495</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.22454</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.02184</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.17238</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.20227</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.02296</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.23316</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.01111</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.23464</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.24248</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.23488</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.02946</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.21334</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.22563</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.21918</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.19156</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29291</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.41673</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32102</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.08422</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.28678</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.79838</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.36866</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.37225</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.51191</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5254800000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.41303</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.41087</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.42926</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.43307</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.42641</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14158</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27639</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27026</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.24821</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39259</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32593</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36685</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.28381</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.40635</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.48287</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.49104</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.40564</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.2581</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47938</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.48415</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.4173</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.5022300000000001</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.40883</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.23864</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.47913</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.37458</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.7612300000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.45061</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41404</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45366</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.25339</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36641</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47561</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.39808</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.38897</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37482</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39601</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.39525</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39941</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.44373</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>1.20388</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.18979</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.44458</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27197</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29276</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36739</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38797</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.37756</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42809</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51012</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.58257</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5981000000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.53679</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.69314</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.72664</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.50041</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5450499999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.5449299999999999</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.71861</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.9723200000000001</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.74464</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.4764</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.52999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.48779</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39706</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44208</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3708</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36821</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.16318</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.26895</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.18861</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.21169</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.15819</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.02134</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26316</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05508</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.07714</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.0868</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.24704</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08879000000000001</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05924</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.20333</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.16483</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.18386</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37819</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.5061100000000001</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.39113</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.44055</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.43085</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39442</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42221</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38929</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.39792</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.42808</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37837</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36861</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.95505</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.53927</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.47504</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.42972</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36416</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36834</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.40094</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.6897799999999999</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.02051</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.67765</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.15399</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.72975</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.5312</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.62573</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.6402899999999999</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.50236</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.40099</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.4123</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40484</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37741</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38191</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38347</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.40357</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37461</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.3868</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36209</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3629</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38304</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36896</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.28462</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.1631</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.27075</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.28163</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.13122</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.17854</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.20255</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.45472</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04459</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.19679</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>1.34476</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.23602</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.18249</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.42833</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.50618</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.20455</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.1408</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.27868</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.14159</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.61333</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.28286</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.1765</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.13343</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26227</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.22621</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.29135</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.28675</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.33697</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38635</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47296</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39076</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38088</v>
       </c>
     </row>
   </sheetData>
